--- a/fhir/finnish-smart/StructureDefinition-fi-smart-practitioner.xlsx
+++ b/fhir/finnish-smart/StructureDefinition-fi-smart-practitioner.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-rc2</t>
+    <t>2.0.0-rc3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-11T17:07:13+03:00</t>
+    <t>2025-06-01T15:36:45+03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/finnish-smart/StructureDefinition-fi-smart-practitioner.xlsx
+++ b/fhir/finnish-smart/StructureDefinition-fi-smart-practitioner.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$54</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="363">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-rc3</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-01T15:36:45+03:00</t>
+    <t>2025-10-26T13:24:16+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -855,14 +852,18 @@
     <t>The name(s) associated with the practitioner.</t>
   </si>
   <si>
-    <t>In some contexts, the real name of the practitioner is obscured. However this is handled, the resource must include at least some useable name for the practitioner in the name.text element</t>
+    <t>The selection of the use property should ensure that there is a single usual name specified, and others use the nickname (alias), old, or other values as appropriate.  ++In general, select the value to be used in the ResourceReference.display based on this:++1. There is more than 1 name+2. Use = usual+3. Period is current to the date of the usage+4. Use = official+5. Other order as decided by internal business rules.</t>
   </si>
   <si>
     <t>The name(s) that a Practitioner is known by. Where there are multiple, the name that the practitioner is usually known as should be used in the display.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ipa-pract-1:To be usable for a wide range of internationally available applications, the Patient.name.text SHOULD be present. {text.exists()}</t>
   </si>
   <si>
     <t>XCN Components</t>
@@ -1270,21 +1271,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1624,7 +1610,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -1736,7 +1722,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -1850,7 +1836,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -1962,7 +1948,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>101</v>
       </c>
@@ -2076,7 +2062,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>107</v>
       </c>
@@ -2190,7 +2176,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -2304,7 +2290,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -2418,7 +2404,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -2532,7 +2518,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>140</v>
       </c>
@@ -2648,7 +2634,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -2762,7 +2748,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>157</v>
       </c>
@@ -2878,7 +2864,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>159</v>
       </c>
@@ -2990,7 +2976,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>166</v>
       </c>
@@ -3104,7 +3090,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>172</v>
       </c>
@@ -3220,7 +3206,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>183</v>
       </c>
@@ -3336,7 +3322,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>195</v>
       </c>
@@ -3452,7 +3438,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>207</v>
       </c>
@@ -3566,7 +3552,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>217</v>
       </c>
@@ -3678,7 +3664,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>226</v>
       </c>
@@ -3792,7 +3778,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>236</v>
       </c>
@@ -3908,7 +3894,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>238</v>
       </c>
@@ -4020,7 +4006,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>239</v>
       </c>
@@ -4134,7 +4120,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>240</v>
       </c>
@@ -4250,7 +4236,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>241</v>
       </c>
@@ -4366,7 +4352,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>242</v>
       </c>
@@ -4482,7 +4468,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>244</v>
       </c>
@@ -4596,7 +4582,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>245</v>
       </c>
@@ -4708,7 +4694,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>246</v>
       </c>
@@ -4822,7 +4808,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>247</v>
       </c>
@@ -4938,7 +4924,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>249</v>
       </c>
@@ -5050,7 +5036,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>250</v>
       </c>
@@ -5164,7 +5150,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>251</v>
       </c>
@@ -5280,7 +5266,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>252</v>
       </c>
@@ -5396,7 +5382,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>253</v>
       </c>
@@ -5512,7 +5498,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>255</v>
       </c>
@@ -5626,7 +5612,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>256</v>
       </c>
@@ -5738,7 +5724,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>257</v>
       </c>
@@ -5852,7 +5838,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>258</v>
       </c>
@@ -5970,7 +5956,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>267</v>
       </c>
@@ -5983,13 +5969,13 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>77</v>
@@ -6071,27 +6057,27 @@
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK40" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AK40" t="s" s="2">
+      <c r="AL40" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AN40" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="41" hidden="true">
-      <c r="A41" t="s" s="2">
-        <v>277</v>
-      </c>
       <c r="B41" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6114,19 +6100,19 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6175,7 +6161,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6190,24 +6176,24 @@
         <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AN41" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="42" hidden="true">
-      <c r="A42" t="s" s="2">
-        <v>286</v>
-      </c>
       <c r="B42" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6230,19 +6216,19 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6291,7 +6277,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6306,24 +6292,24 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AN42" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="43" hidden="true">
-      <c r="A43" t="s" s="2">
-        <v>295</v>
-      </c>
       <c r="B43" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6349,14 +6335,14 @@
         <v>108</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6384,11 +6370,11 @@
         <v>178</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="Z43" t="s" s="2">
-        <v>300</v>
-      </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
       </c>
@@ -6405,7 +6391,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6420,24 +6406,24 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AN43" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="44" hidden="true">
-      <c r="A44" t="s" s="2">
-        <v>304</v>
-      </c>
       <c r="B44" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6460,17 +6446,17 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6519,7 +6505,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6534,24 +6520,24 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AN44" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="45" hidden="true">
-      <c r="A45" t="s" s="2">
-        <v>312</v>
-      </c>
       <c r="B45" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6574,17 +6560,17 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6633,7 +6619,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6651,21 +6637,21 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AM45" t="s" s="2">
+      <c r="AN45" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AN45" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="46" hidden="true">
-      <c r="A46" t="s" s="2">
-        <v>319</v>
-      </c>
       <c r="B46" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6688,13 +6674,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6745,7 +6731,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6760,24 +6746,24 @@
         <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AN46" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="47" hidden="true">
-      <c r="A47" t="s" s="2">
-        <v>326</v>
-      </c>
       <c r="B47" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6884,12 +6870,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6998,16 +6984,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7029,10 +7015,10 @@
         <v>134</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>137</v>
@@ -7087,7 +7073,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7114,12 +7100,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7145,14 +7131,14 @@
         <v>146</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7201,7 +7187,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7219,21 +7205,21 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AM50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="51" hidden="true">
-      <c r="A51" t="s" s="2">
-        <v>338</v>
-      </c>
       <c r="B51" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7259,10 +7245,10 @@
         <v>185</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7289,14 +7275,14 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="Y51" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="Y51" t="s" s="2">
+      <c r="Z51" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>343</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7313,7 +7299,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>88</v>
@@ -7331,21 +7317,21 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AN51" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="52" hidden="true">
-      <c r="A52" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="B52" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7371,14 +7357,14 @@
         <v>219</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7427,7 +7413,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7445,21 +7431,21 @@
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AN52" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="53" hidden="true">
-      <c r="A53" t="s" s="2">
-        <v>351</v>
-      </c>
       <c r="B53" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7482,13 +7468,13 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7539,7 +7525,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7557,21 +7543,21 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AM53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="54" hidden="true">
-      <c r="A54" t="s" s="2">
-        <v>356</v>
-      </c>
       <c r="B54" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7597,16 +7583,16 @@
         <v>185</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7655,7 +7641,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7670,37 +7656,19 @@
         <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AL54" t="s" s="2">
+      <c r="AM54" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN54">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI53">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>